--- a/data/data_monitoreo_la_colorada.xlsx
+++ b/data/data_monitoreo_la_colorada.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>157</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>156</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>138</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5">
@@ -477,37 +477,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZAVALETA MANAY JORGE LUIS</t>
+          <t>ROMERO CHANAME YOSSELY TRINIDAD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAMACHO LINARES JUDITH ARLETT</t>
+          <t>SEVERINO AVALOS MARJORIE ISABEL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEVERINO AVALOS MARJORIE ISABEL</t>
+          <t>ZAVALETA MANAY JORGE LUIS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
@@ -517,17 +517,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ROMERO CHANAME YOSSELY TRINIDAD</t>
+          <t>CAMACHO LINARES JUDITH ARLETT</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15">

--- a/data/data_monitoreo_la_colorada.xlsx
+++ b/data/data_monitoreo_la_colorada.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>225</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4">
@@ -477,53 +477,53 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ROMERO CHANAME YOSSELY TRINIDAD</t>
+          <t>SEVERINO AVALOS MARJORIE ISABEL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEVERINO AVALOS MARJORIE ISABEL</t>
+          <t>ZAVALETA MANAY JORGE LUIS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZAVALETA MANAY JORGE LUIS</t>
+          <t>HIDALGO CUBAS LUISA YVONE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HUMPIRE CASTILLO IRWIN DEIMER</t>
+          <t>ROMERO CHANAME YOSSELY TRINIDAD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAMACHO LINARES JUDITH ARLETT</t>
+          <t>HUMPIRE CASTILLO IRWIN DEIMER</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -533,31 +533,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HIDALGO CUBAS LUISA YVONE</t>
+          <t>CAMACHO LINARES JUDITH ARLETT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZEVALLOS PACHECO ZOILA XIMENA</t>
+          <t>BALLENA ESQUÉN ASTRID CAROLINA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BALLENA ESQUÉN ASTRID CAROLINA</t>
+          <t>ZEVALLOS PACHECO ZOILA XIMENA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">

--- a/data/data_monitoreo_la_colorada.xlsx
+++ b/data/data_monitoreo_la_colorada.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZAVALETA MANAY JORGE LUIS</t>
+          <t>HIDALGO CUBAS LUISA YVONE</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -503,11 +503,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HIDALGO CUBAS LUISA YVONE</t>
+          <t>ZAVALETA MANAY JORGE LUIS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9">

--- a/data/data_monitoreo_la_colorada.xlsx
+++ b/data/data_monitoreo_la_colorada.xlsx
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
